--- a/models/Qassim-Cement-3040-Valuation-Model.xlsx
+++ b/models/Qassim-Cement-3040-Valuation-Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Qassim Cement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6B117E-6197-4608-97FE-D2A2F2A2F5B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B078D759-65BB-45F1-90AA-CF5DF24903AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="1845" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FSM" sheetId="4" r:id="rId1"/>
@@ -251,7 +251,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="310">
   <si>
     <t>Company Name</t>
   </si>
@@ -1138,9 +1138,6 @@
     <t>Total Debt</t>
   </si>
   <si>
-    <t>Interest Coverage Ratio EBT / Finance Cost</t>
-  </si>
-  <si>
     <t>Leverage Ratios</t>
   </si>
   <si>
@@ -1148,6 +1145,42 @@
   </si>
   <si>
     <t>Liquidity Ratios</t>
+  </si>
+  <si>
+    <t>Returns &amp; Profitability</t>
+  </si>
+  <si>
+    <t>Return on Assets (ROA)</t>
+  </si>
+  <si>
+    <t>Return on Equity (ROE)</t>
+  </si>
+  <si>
+    <t>Interest Coverage Ratio EBIT / Finance Cost</t>
+  </si>
+  <si>
+    <t>Net profit margin</t>
+  </si>
+  <si>
+    <t>Asset turnover</t>
+  </si>
+  <si>
+    <t>Equity multiplier (leverage)</t>
+  </si>
+  <si>
+    <t>ROE (DuPont)</t>
+  </si>
+  <si>
+    <t>Check: DuPont = direct ROE</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>DuPont</t>
   </si>
 </sst>
 </file>
@@ -3206,7 +3239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F370973C-64E9-46C3-8015-F083BA56F634}">
-  <dimension ref="A1:K304"/>
+  <dimension ref="A1:L317"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="1.7109375" style="6" customWidth="1"/>
@@ -4540,23 +4573,23 @@
       </c>
       <c r="G56" s="19">
         <f>G143</f>
-        <v>117296841.66299999</v>
+        <v>117296841.66299996</v>
       </c>
       <c r="H56" s="19">
         <f t="shared" ref="H56:K56" si="34">H143</f>
-        <v>131372462.66255999</v>
+        <v>131372462.66255996</v>
       </c>
       <c r="I56" s="19">
         <f t="shared" si="34"/>
-        <v>144509708.92881596</v>
+        <v>151171713.19570589</v>
       </c>
       <c r="J56" s="19">
         <f t="shared" si="34"/>
-        <v>156070485.64312124</v>
+        <v>241652928.23200494</v>
       </c>
       <c r="K56" s="19">
         <f t="shared" si="34"/>
-        <v>165434714.7817086</v>
+        <v>380127683.06239074</v>
       </c>
     </row>
     <row r="57" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4585,15 +4618,15 @@
       </c>
       <c r="I57" s="12">
         <f t="shared" ref="I57" si="37">SUM(I51:I56)</f>
-        <v>1734719554.9016161</v>
+        <v>1741381559.1685059</v>
       </c>
       <c r="J57" s="12">
         <f t="shared" ref="J57" si="38">SUM(J51:J56)</f>
-        <v>1866884983.4537454</v>
+        <v>1952467426.042629</v>
       </c>
       <c r="K57" s="12">
         <f t="shared" ref="K57" si="39">SUM(K51:K56)</f>
-        <v>1973938980.5809703</v>
+        <v>2188631948.8616524</v>
       </c>
     </row>
     <row r="58" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4927,15 +4960,15 @@
       </c>
       <c r="I69" s="14">
         <f t="shared" si="53"/>
-        <v>3935366756.0521021</v>
+        <v>3942028760.3189917</v>
       </c>
       <c r="J69" s="14">
         <f t="shared" si="53"/>
-        <v>4165882747.5200777</v>
+        <v>4251465190.1089611</v>
       </c>
       <c r="K69" s="14">
         <f t="shared" si="53"/>
-        <v>4358806706.3623543</v>
+        <v>4573499674.6430359</v>
       </c>
     </row>
     <row r="70" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5194,23 +5227,23 @@
       <c r="F80" s="10"/>
       <c r="G80" s="19">
         <f>G259</f>
-        <v>235723320.62769592</v>
+        <v>29509852.901532277</v>
       </c>
       <c r="H80" s="19">
         <f t="shared" ref="H80:K80" si="60">H259</f>
-        <v>460020743.86855549</v>
+        <v>27575987.727222592</v>
       </c>
       <c r="I80" s="19">
         <f t="shared" si="60"/>
-        <v>669350551.75908399</v>
+        <v>0</v>
       </c>
       <c r="J80" s="19">
         <f t="shared" si="60"/>
-        <v>853674851.01949418</v>
+        <v>0</v>
       </c>
       <c r="K80" s="19">
         <f t="shared" si="60"/>
-        <v>1003734198.5306759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5231,23 +5264,23 @@
       </c>
       <c r="G81" s="12">
         <f t="shared" si="61"/>
-        <v>636641048.46328413</v>
+        <v>430427580.73712051</v>
       </c>
       <c r="H81" s="12">
         <f t="shared" si="61"/>
-        <v>890315970.83974266</v>
+        <v>457871214.69840968</v>
       </c>
       <c r="I81" s="12">
         <f t="shared" si="61"/>
-        <v>1127067499.9560816</v>
+        <v>457716948.1969977</v>
       </c>
       <c r="J81" s="12">
         <f t="shared" si="61"/>
-        <v>1335526506.9782171</v>
+        <v>481851655.95872283</v>
       </c>
       <c r="K81" s="12">
         <f t="shared" si="61"/>
-        <v>1505139818.4384623</v>
+        <v>501405619.90778637</v>
       </c>
     </row>
     <row r="82" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5437,23 +5470,23 @@
       </c>
       <c r="G89" s="25">
         <f t="shared" si="67"/>
-        <v>733645338.12703168</v>
+        <v>527431870.40086806</v>
       </c>
       <c r="H89" s="25">
         <f t="shared" ref="H89:K89" si="68">H81+H87</f>
-        <v>991459502.2930094</v>
+        <v>559014746.15167642</v>
       </c>
       <c r="I89" s="25">
         <f t="shared" si="68"/>
-        <v>1232531606.3170373</v>
+        <v>563181054.55795348</v>
       </c>
       <c r="J89" s="25">
         <f t="shared" si="68"/>
-        <v>1445497948.6128526</v>
+        <v>591823097.59335828</v>
       </c>
       <c r="K89" s="25">
         <f t="shared" si="68"/>
-        <v>1619810582.5749302</v>
+        <v>616076384.0442543</v>
       </c>
     </row>
     <row r="90" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5662,23 +5695,23 @@
       </c>
       <c r="G97" s="19">
         <f>G212</f>
-        <v>347392005.51507765</v>
+        <v>553605473.24124122</v>
       </c>
       <c r="H97" s="19">
         <f t="shared" ref="H97:K97" si="71">H212</f>
-        <v>362474091.40942228</v>
+        <v>794918847.55075502</v>
       </c>
       <c r="I97" s="19">
         <f t="shared" si="71"/>
-        <v>378711944.73506498</v>
+        <v>1054724500.7610389</v>
       </c>
       <c r="J97" s="19">
         <f t="shared" si="71"/>
-        <v>396261593.90722531</v>
+        <v>1335518887.5156031</v>
       </c>
       <c r="K97" s="19">
         <f t="shared" si="71"/>
-        <v>414872918.78742403</v>
+        <v>1633300085.5987821</v>
       </c>
     </row>
     <row r="98" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5699,23 +5732,23 @@
       </c>
       <c r="G98" s="12">
         <f t="shared" si="72"/>
-        <v>2671515210.5150776</v>
+        <v>2877728678.2412415</v>
       </c>
       <c r="H98" s="12">
         <f t="shared" ref="H98" si="73">SUM(H92:H97)</f>
-        <v>2686597296.4094224</v>
+        <v>3119042052.550755</v>
       </c>
       <c r="I98" s="12">
         <f t="shared" ref="I98" si="74">SUM(I92:I97)</f>
-        <v>2702835149.735065</v>
+        <v>3378847705.7610388</v>
       </c>
       <c r="J98" s="12">
         <f t="shared" ref="J98" si="75">SUM(J92:J97)</f>
-        <v>2720384798.9072251</v>
+        <v>3659642092.5156031</v>
       </c>
       <c r="K98" s="12">
         <f t="shared" ref="K98" si="76">SUM(K92:K97)</f>
-        <v>2738996123.7874241</v>
+        <v>3957423290.5987821</v>
       </c>
     </row>
     <row r="99" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5753,15 +5786,15 @@
       </c>
       <c r="I100" s="14">
         <f t="shared" si="78"/>
-        <v>3935366756.0521021</v>
+        <v>3942028760.3189921</v>
       </c>
       <c r="J100" s="14">
         <f t="shared" si="78"/>
-        <v>4165882747.5200777</v>
+        <v>4251465190.1089611</v>
       </c>
       <c r="K100" s="14">
         <f t="shared" si="78"/>
-        <v>4358806706.3623543</v>
+        <v>4573499674.6430359</v>
       </c>
     </row>
     <row r="101" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6567,23 +6600,23 @@
       <c r="F137" s="204"/>
       <c r="G137" s="204">
         <f>-G269</f>
-        <v>-261203725.78647393</v>
+        <v>-54990258.060310304</v>
       </c>
       <c r="H137" s="204">
         <f t="shared" ref="H137:K137" si="93">-H269</f>
-        <v>-286559631.99254775</v>
+        <v>-60328343.577378482</v>
       </c>
       <c r="I137" s="204">
         <f t="shared" si="93"/>
-        <v>-308519213.18721199</v>
+        <v>-64951413.302570954</v>
       </c>
       <c r="J137" s="204">
         <f t="shared" si="93"/>
-        <v>-333443334.27104503</v>
+        <v>-70198596.688641056</v>
       </c>
       <c r="K137" s="204">
         <f t="shared" si="93"/>
-        <v>-353615172.72377485</v>
+        <v>-74445299.520794719</v>
       </c>
     </row>
     <row r="138" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6595,23 +6628,23 @@
       <c r="F138" s="204"/>
       <c r="G138" s="204">
         <f>G260</f>
-        <v>235723320.62769592</v>
+        <v>29509852.901532277</v>
       </c>
       <c r="H138" s="204">
         <f t="shared" ref="H138:K138" si="94">H260</f>
-        <v>224297423.24085957</v>
+        <v>-1933865.1743096858</v>
       </c>
       <c r="I138" s="204">
         <f t="shared" si="94"/>
-        <v>209329807.8905285</v>
+        <v>-27575987.727222592</v>
       </c>
       <c r="J138" s="204">
         <f t="shared" si="94"/>
-        <v>184324299.26041019</v>
+        <v>0</v>
       </c>
       <c r="K138" s="204">
         <f t="shared" si="94"/>
-        <v>150059347.51118171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6623,7 +6656,7 @@
       <c r="F139" s="207"/>
       <c r="G139" s="207">
         <f>SUM(G135:G138)</f>
-        <v>-26379103.183661431</v>
+        <v>-26379103.183661453</v>
       </c>
       <c r="H139" s="207">
         <f t="shared" ref="H139:K139" si="95">SUM(H135:H138)</f>
@@ -6631,15 +6664,15 @@
       </c>
       <c r="I139" s="207">
         <f t="shared" si="95"/>
-        <v>-100064196.21114236</v>
+        <v>-93402191.944252402</v>
       </c>
       <c r="J139" s="207">
         <f t="shared" si="95"/>
-        <v>-150066395.91864645</v>
+        <v>-71145957.596652672</v>
       </c>
       <c r="K139" s="207">
         <f t="shared" si="95"/>
-        <v>-204562873.16752112</v>
+        <v>-75452347.475722685</v>
       </c>
     </row>
     <row r="140" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6662,7 +6695,7 @@
       <c r="F141" s="207"/>
       <c r="G141" s="207">
         <f>G125+G131+G139</f>
-        <v>12546551.662999988</v>
+        <v>12546551.662999965</v>
       </c>
       <c r="H141" s="207">
         <f>H125+H131+H139</f>
@@ -6670,15 +6703,15 @@
       </c>
       <c r="I141" s="207">
         <f>I125+I131+I139</f>
-        <v>13137246.266255975</v>
+        <v>19799250.533145934</v>
       </c>
       <c r="J141" s="207">
         <f>J125+J131+J139</f>
-        <v>11560776.714305282</v>
+        <v>90481215.036299065</v>
       </c>
       <c r="K141" s="207">
         <f>K125+K131+K139</f>
-        <v>9364229.1385873556</v>
+        <v>138474754.8303858</v>
       </c>
     </row>
     <row r="142" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6694,19 +6727,19 @@
       </c>
       <c r="H142" s="207">
         <f>G56</f>
-        <v>117296841.66299999</v>
+        <v>117296841.66299996</v>
       </c>
       <c r="I142" s="207">
         <f>H56</f>
-        <v>131372462.66255999</v>
+        <v>131372462.66255996</v>
       </c>
       <c r="J142" s="207">
         <f>I56</f>
-        <v>144509708.92881596</v>
+        <v>151171713.19570589</v>
       </c>
       <c r="K142" s="207">
         <f>J56</f>
-        <v>156070485.64312124</v>
+        <v>241652928.23200494</v>
       </c>
     </row>
     <row r="143" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6718,23 +6751,23 @@
       <c r="F143" s="207"/>
       <c r="G143" s="207">
         <f>G141+G142</f>
-        <v>117296841.66299999</v>
+        <v>117296841.66299996</v>
       </c>
       <c r="H143" s="207">
         <f t="shared" ref="H143:K143" si="96">H141+H142</f>
-        <v>131372462.66255999</v>
+        <v>131372462.66255996</v>
       </c>
       <c r="I143" s="207">
         <f t="shared" si="96"/>
-        <v>144509708.92881596</v>
+        <v>151171713.19570589</v>
       </c>
       <c r="J143" s="207">
         <f t="shared" si="96"/>
-        <v>156070485.64312124</v>
+        <v>241652928.23200494</v>
       </c>
       <c r="K143" s="207">
         <f t="shared" si="96"/>
-        <v>165434714.7817086</v>
+        <v>380127683.06239074</v>
       </c>
     </row>
     <row r="144" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8308,19 +8341,19 @@
       </c>
       <c r="H208" s="188">
         <f t="shared" si="144"/>
-        <v>347392005.51507765</v>
+        <v>553605473.24124122</v>
       </c>
       <c r="I208" s="188">
         <f t="shared" si="144"/>
-        <v>362474091.40942228</v>
+        <v>794918847.55075502</v>
       </c>
       <c r="J208" s="188">
         <f t="shared" si="144"/>
-        <v>378711944.73506498</v>
+        <v>1054724500.7610389</v>
       </c>
       <c r="K208" s="188">
         <f t="shared" si="144"/>
-        <v>396261593.90722531</v>
+        <v>1335518887.5156031</v>
       </c>
     </row>
     <row r="209" spans="3:11" x14ac:dyDescent="0.25">
@@ -8375,23 +8408,23 @@
       </c>
       <c r="G210" s="188">
         <f>G209*G214</f>
-        <v>261203725.78647393</v>
+        <v>54990258.060310304</v>
       </c>
       <c r="H210" s="188">
         <f t="shared" ref="H210:K210" si="146">H209*H214</f>
-        <v>286559631.99254775</v>
+        <v>60328343.577378482</v>
       </c>
       <c r="I210" s="188">
         <f t="shared" si="146"/>
-        <v>308519213.18721199</v>
+        <v>64951413.302570954</v>
       </c>
       <c r="J210" s="188">
         <f t="shared" si="146"/>
-        <v>333443334.27104503</v>
+        <v>70198596.688641056</v>
       </c>
       <c r="K210" s="188">
         <f t="shared" si="146"/>
-        <v>353615172.72377485</v>
+        <v>74445299.520794719</v>
       </c>
     </row>
     <row r="211" spans="3:11" x14ac:dyDescent="0.25">
@@ -8425,23 +8458,23 @@
       </c>
       <c r="G212" s="188">
         <f>G208+G209-G210</f>
-        <v>347392005.51507765</v>
+        <v>553605473.24124122</v>
       </c>
       <c r="H212" s="188">
         <f t="shared" ref="H212:K212" si="147">H208+H209-H210</f>
-        <v>362474091.40942228</v>
+        <v>794918847.55075502</v>
       </c>
       <c r="I212" s="188">
         <f t="shared" si="147"/>
-        <v>378711944.73506498</v>
+        <v>1054724500.7610389</v>
       </c>
       <c r="J212" s="188">
         <f t="shared" si="147"/>
-        <v>396261593.90722531</v>
+        <v>1335518887.5156031</v>
       </c>
       <c r="K212" s="188">
         <f t="shared" si="147"/>
-        <v>414872918.78742403</v>
+        <v>1633300085.5987821</v>
       </c>
     </row>
     <row r="213" spans="3:11" x14ac:dyDescent="0.25">
@@ -8471,23 +8504,23 @@
         <v>1.3458399501542051</v>
       </c>
       <c r="G214" s="215">
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="H214" s="215">
         <f t="shared" ref="H214:K214" si="149">G214</f>
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="I214" s="215">
         <f t="shared" si="149"/>
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="J214" s="215">
         <f t="shared" si="149"/>
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
       <c r="K214" s="215">
         <f t="shared" si="149"/>
-        <v>0.95</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="216" spans="3:11" x14ac:dyDescent="0.25">
@@ -9615,23 +9648,23 @@
       <c r="F258" s="188"/>
       <c r="G258" s="188">
         <f>F56+G125+G131+(G135+G136+G137)</f>
-        <v>-118426478.96469593</v>
+        <v>87786988.761467695</v>
       </c>
       <c r="H258" s="188">
         <f>G56+H125+H131+(H135+H136+H137)</f>
-        <v>-92924960.578299582</v>
+        <v>133306327.83686967</v>
       </c>
       <c r="I258" s="188">
         <f>H56+I125+I131+(I135+I136+I137)</f>
-        <v>-64820098.961712539</v>
+        <v>178747700.92292851</v>
       </c>
       <c r="J258" s="188">
         <f>I56+J125+J131+(J135+J136+J137)</f>
-        <v>-28253813.617288947</v>
+        <v>241652928.23200494</v>
       </c>
       <c r="K258" s="188">
         <f>J56+K125+K131+(K135+K136+K137)</f>
-        <v>15375367.270526886</v>
+        <v>380127683.0623908</v>
       </c>
     </row>
     <row r="259" spans="3:11" x14ac:dyDescent="0.25">
@@ -9645,23 +9678,23 @@
       </c>
       <c r="G259" s="188">
         <f>MAX(0,F259-(G258-G257))</f>
-        <v>235723320.62769592</v>
+        <v>29509852.901532277</v>
       </c>
       <c r="H259" s="188">
         <f t="shared" ref="H259:K259" si="181">MAX(0,G259-(H258-H257))</f>
-        <v>460020743.86855549</v>
+        <v>27575987.727222592</v>
       </c>
       <c r="I259" s="188">
         <f t="shared" si="181"/>
-        <v>669350551.75908399</v>
+        <v>0</v>
       </c>
       <c r="J259" s="188">
         <f t="shared" si="181"/>
-        <v>853674851.01949418</v>
+        <v>0</v>
       </c>
       <c r="K259" s="188">
         <f t="shared" si="181"/>
-        <v>1003734198.5306759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260" spans="3:11" x14ac:dyDescent="0.25">
@@ -9673,23 +9706,23 @@
       <c r="F260" s="188"/>
       <c r="G260" s="188">
         <f>G259-F259</f>
-        <v>235723320.62769592</v>
+        <v>29509852.901532277</v>
       </c>
       <c r="H260" s="188">
         <f t="shared" ref="H260:K260" si="182">H259-G259</f>
-        <v>224297423.24085957</v>
+        <v>-1933865.1743096858</v>
       </c>
       <c r="I260" s="188">
         <f t="shared" si="182"/>
-        <v>209329807.8905285</v>
+        <v>-27575987.727222592</v>
       </c>
       <c r="J260" s="188">
         <f t="shared" si="182"/>
-        <v>184324299.26041019</v>
+        <v>0</v>
       </c>
       <c r="K260" s="188">
         <f t="shared" si="182"/>
-        <v>150059347.51118171</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="3:11" x14ac:dyDescent="0.25">
@@ -9856,23 +9889,23 @@
       </c>
       <c r="G268" s="268">
         <f>G210</f>
-        <v>261203725.78647393</v>
+        <v>54990258.060310304</v>
       </c>
       <c r="H268" s="268">
         <f>H210</f>
-        <v>286559631.99254775</v>
+        <v>60328343.577378482</v>
       </c>
       <c r="I268" s="268">
         <f>I210</f>
-        <v>308519213.18721199</v>
+        <v>64951413.302570954</v>
       </c>
       <c r="J268" s="268">
         <f>J210</f>
-        <v>333443334.27104503</v>
+        <v>70198596.688641056</v>
       </c>
       <c r="K268" s="268">
         <f>K210</f>
-        <v>353615172.72377485</v>
+        <v>74445299.520794719</v>
       </c>
     </row>
     <row r="269" spans="3:11" x14ac:dyDescent="0.25">
@@ -9890,23 +9923,23 @@
       </c>
       <c r="G269" s="268">
         <f>G268</f>
-        <v>261203725.78647393</v>
+        <v>54990258.060310304</v>
       </c>
       <c r="H269" s="268">
         <f t="shared" ref="H269:K269" si="188">H268</f>
-        <v>286559631.99254775</v>
+        <v>60328343.577378482</v>
       </c>
       <c r="I269" s="268">
         <f t="shared" si="188"/>
-        <v>308519213.18721199</v>
+        <v>64951413.302570954</v>
       </c>
       <c r="J269" s="268">
         <f t="shared" si="188"/>
-        <v>333443334.27104503</v>
+        <v>70198596.688641056</v>
       </c>
       <c r="K269" s="268">
         <f t="shared" si="188"/>
-        <v>353615172.72377485</v>
+        <v>74445299.520794719</v>
       </c>
     </row>
     <row r="270" spans="3:11" x14ac:dyDescent="0.25">
@@ -10348,7 +10381,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="289" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="289" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C289" s="43" t="s">
         <v>43</v>
       </c>
@@ -10385,371 +10418,730 @@
         <v>47848</v>
       </c>
     </row>
-    <row r="291" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="291" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C291" s="13" t="s">
         <v>294</v>
       </c>
       <c r="D291" s="162">
-        <f>D75 + D79 + D86+D80</f>
+        <f t="shared" ref="D291:K291" si="204">D75 + D79 + D86+D80</f>
         <v>666527</v>
       </c>
       <c r="E291" s="162">
-        <f>E75 + E79 + E86+E80</f>
+        <f t="shared" si="204"/>
         <v>2645087</v>
       </c>
       <c r="F291" s="162">
-        <f>F75 + F79 + F86+F80</f>
+        <f t="shared" si="204"/>
         <v>102913329</v>
       </c>
       <c r="G291" s="162">
-        <f>G75 + G79 + G86+G80</f>
-        <v>338573985.80591464</v>
+        <f t="shared" si="204"/>
+        <v>132360518.07975098</v>
       </c>
       <c r="H291" s="162">
-        <f>H75 + H79 + H86+H80</f>
-        <v>563014602.49726975</v>
+        <f t="shared" si="204"/>
+        <v>130569846.3559369</v>
       </c>
       <c r="I291" s="162">
-        <f>I75 + I79 + I86+I80</f>
-        <v>772499613.6115613</v>
+        <f t="shared" si="204"/>
+        <v>103149061.85247727</v>
       </c>
       <c r="J291" s="162">
-        <f>J75 + J79 + J86+J80</f>
-        <v>956988945.63323939</v>
+        <f t="shared" si="204"/>
+        <v>103314094.61374521</v>
       </c>
       <c r="K291" s="162">
-        <f>K75 + K79 + K86+K80</f>
-        <v>1107220382.4789295</v>
-      </c>
-    </row>
-    <row r="292" spans="3:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="204"/>
+        <v>103486183.9482536</v>
+      </c>
+    </row>
+    <row r="292" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C292" s="13" t="s">
         <v>287</v>
       </c>
       <c r="D292" s="162">
-        <f>D291 - D56</f>
+        <f t="shared" ref="D292:K292" si="205">D291 - D56</f>
         <v>-39322567</v>
       </c>
       <c r="E292" s="162">
-        <f>E291 - E56</f>
+        <f t="shared" si="205"/>
         <v>-284157270</v>
       </c>
       <c r="F292" s="162">
-        <f>F291 - F56</f>
+        <f t="shared" si="205"/>
         <v>-1836961</v>
       </c>
       <c r="G292" s="162">
-        <f>G291 - G56</f>
-        <v>221277144.14291465</v>
+        <f t="shared" si="205"/>
+        <v>15063676.416751027</v>
       </c>
       <c r="H292" s="162">
-        <f>H291 - H56</f>
-        <v>431642139.83470976</v>
+        <f t="shared" si="205"/>
+        <v>-802616.30662305653</v>
       </c>
       <c r="I292" s="162">
-        <f>I291 - I56</f>
-        <v>627989904.68274534</v>
+        <f t="shared" si="205"/>
+        <v>-48022651.343228623</v>
       </c>
       <c r="J292" s="162">
-        <f>J291 - J56</f>
-        <v>800918459.99011815</v>
+        <f t="shared" si="205"/>
+        <v>-138338833.61825973</v>
       </c>
       <c r="K292" s="162">
-        <f>K291 - K56</f>
-        <v>941785667.69722092</v>
-      </c>
-    </row>
-    <row r="294" spans="3:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="205"/>
+        <v>-276641499.11413717</v>
+      </c>
+    </row>
+    <row r="294" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C294" s="13" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="295" spans="3:11" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="295" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C295" s="17" t="s">
         <v>288</v>
       </c>
       <c r="D295" s="269">
-        <f>D292/D34</f>
+        <f t="shared" ref="D295:K295" si="206">D292/D34</f>
         <v>-0.21592849859472232</v>
       </c>
       <c r="E295" s="269">
-        <f>E292/E34</f>
+        <f t="shared" si="206"/>
         <v>-0.74631178226961903</v>
       </c>
       <c r="F295" s="269">
-        <f>F292/F34</f>
+        <f t="shared" si="206"/>
         <v>-4.5951459974541854E-3</v>
       </c>
       <c r="G295" s="269">
-        <f>G292/G34</f>
-        <v>0.48435155403762686</v>
+        <f t="shared" si="206"/>
+        <v>3.297274605668727E-2</v>
       </c>
       <c r="H295" s="269">
-        <f>H292/H34</f>
-        <v>0.85579409880867074</v>
+        <f t="shared" si="206"/>
+        <v>-1.5913050080760178E-3</v>
       </c>
       <c r="I295" s="269">
-        <f>I292/I34</f>
-        <v>1.1485124498240085</v>
+        <f t="shared" si="206"/>
+        <v>-8.7827228638522964E-2</v>
       </c>
       <c r="J295" s="269">
-        <f>J292/J34</f>
-        <v>1.3562744898199497</v>
+        <f t="shared" si="206"/>
+        <v>-0.23426283743067564</v>
       </c>
       <c r="K295" s="269">
-        <f>K292/K34</f>
-        <v>1.5045461068976027</v>
-      </c>
-    </row>
-    <row r="296" spans="3:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="206"/>
+        <v>-0.44194757339660867</v>
+      </c>
+      <c r="L295" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="296" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C296" s="17" t="s">
         <v>289</v>
       </c>
       <c r="D296" s="1">
-        <f xml:space="preserve"> D291/ D69</f>
+        <f t="shared" ref="D296:K296" si="207" xml:space="preserve"> D291/ D69</f>
         <v>3.6930668870553901E-4</v>
       </c>
       <c r="E296" s="1">
-        <f xml:space="preserve"> E291/ E69</f>
+        <f t="shared" si="207"/>
         <v>8.4857695604603333E-4</v>
       </c>
       <c r="F296" s="1">
-        <f xml:space="preserve"> F291/ F69</f>
+        <f t="shared" si="207"/>
         <v>3.298515130723037E-2</v>
       </c>
       <c r="G296" s="1">
-        <f xml:space="preserve"> G291/ G69</f>
-        <v>9.9429668871539492E-2</v>
+        <f t="shared" si="207"/>
+        <v>3.8870566068473035E-2</v>
       </c>
       <c r="H296" s="1">
-        <f xml:space="preserve"> H291/ H69</f>
-        <v>0.15307392824816995</v>
+        <f t="shared" si="207"/>
+        <v>3.5499681897789119E-2</v>
       </c>
       <c r="I296" s="1">
-        <f xml:space="preserve"> I291/ I69</f>
-        <v>0.19629672696288178</v>
+        <f t="shared" si="207"/>
+        <v>2.6166491449983835E-2</v>
       </c>
       <c r="J296" s="1">
-        <f xml:space="preserve"> J291/ J69</f>
-        <v>0.22972056671612481</v>
+        <f t="shared" si="207"/>
+        <v>2.4300821009685222E-2</v>
       </c>
       <c r="K296" s="1">
-        <f xml:space="preserve"> K291/ K69</f>
-        <v>0.25401915181574114</v>
-      </c>
-    </row>
-    <row r="297" spans="3:11" x14ac:dyDescent="0.25">
+        <f t="shared" si="207"/>
+        <v>2.2627351330538961E-2</v>
+      </c>
+      <c r="L296" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="297" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C297" s="17" t="s">
         <v>290</v>
       </c>
       <c r="D297" s="269">
-        <f>D292/D97</f>
+        <f t="shared" ref="D297:K297" si="208">D292/D97</f>
         <v>-9.5669391417608093E-2</v>
       </c>
       <c r="E297" s="269">
-        <f>E292/E97</f>
+        <f t="shared" si="208"/>
         <v>-0.66869084864202422</v>
       </c>
       <c r="F297" s="269">
-        <f>F292/F97</f>
+        <f t="shared" si="208"/>
         <v>-5.5057443621546803E-3</v>
       </c>
       <c r="G297" s="269">
-        <f>G292/G97</f>
-        <v>0.63696671377001701</v>
+        <f t="shared" si="208"/>
+        <v>2.7210129135025411E-2</v>
       </c>
       <c r="H297" s="269">
-        <f>H292/H97</f>
-        <v>1.1908220478775149</v>
+        <f t="shared" si="208"/>
+        <v>-1.0096833269157201E-3</v>
       </c>
       <c r="I297" s="269">
-        <f>I292/I97</f>
-        <v>1.6582257660821007</v>
+        <f t="shared" si="208"/>
+        <v>-4.5530990612788237E-2</v>
       </c>
       <c r="J297" s="269">
-        <f>J292/J97</f>
-        <v>2.0211861868643095</v>
+        <f t="shared" si="208"/>
+        <v>-0.103584333333993</v>
       </c>
       <c r="K297" s="269">
-        <f>K292/K97</f>
-        <v>2.270058191433268</v>
-      </c>
-    </row>
-    <row r="298" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C298" s="13" t="s">
+        <f t="shared" si="208"/>
+        <v>-0.16937579416872311</v>
+      </c>
+      <c r="L297" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="298" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C298" s="17"/>
+      <c r="D298" s="269"/>
+      <c r="E298" s="269"/>
+      <c r="F298" s="269"/>
+      <c r="G298" s="269"/>
+      <c r="H298" s="269"/>
+      <c r="I298" s="269"/>
+      <c r="J298" s="269"/>
+      <c r="K298" s="269"/>
+    </row>
+    <row r="299" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C299" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="D299" s="1"/>
+      <c r="E299" s="1"/>
+      <c r="F299" s="1"/>
+      <c r="G299" s="1"/>
+      <c r="H299" s="1"/>
+      <c r="I299" s="1"/>
+      <c r="J299" s="1"/>
+      <c r="K299" s="1"/>
+    </row>
+    <row r="300" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C300" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="D300" s="269">
+        <f t="shared" ref="D300:K300" si="209">D23/ABS(D28)</f>
+        <v>43.646272915512931</v>
+      </c>
+      <c r="E300" s="269">
+        <f t="shared" si="209"/>
+        <v>69.062139074572443</v>
+      </c>
+      <c r="F300" s="269">
+        <f t="shared" si="209"/>
+        <v>60.114135699581482</v>
+      </c>
+      <c r="G300" s="269">
+        <f t="shared" si="209"/>
+        <v>67.041013734978748</v>
+      </c>
+      <c r="H300" s="269">
+        <f t="shared" si="209"/>
+        <v>71.876792675225701</v>
+      </c>
+      <c r="I300" s="269">
+        <f t="shared" si="209"/>
+        <v>75.684630154587666</v>
+      </c>
+      <c r="J300" s="269">
+        <f t="shared" si="209"/>
+        <v>80.036496388476451</v>
+      </c>
+      <c r="K300" s="269">
+        <f t="shared" si="209"/>
+        <v>83.107284413177169</v>
+      </c>
+      <c r="L300" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="301" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C301" s="17"/>
+      <c r="D301" s="269"/>
+      <c r="E301" s="269"/>
+      <c r="F301" s="269"/>
+      <c r="G301" s="269"/>
+      <c r="H301" s="269"/>
+      <c r="I301" s="269"/>
+      <c r="J301" s="269"/>
+      <c r="K301" s="269"/>
+    </row>
+    <row r="302" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C302" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="D298" s="1"/>
-      <c r="E298" s="1"/>
-      <c r="F298" s="1"/>
-      <c r="G298" s="1"/>
-      <c r="H298" s="1"/>
-      <c r="I298" s="1"/>
-      <c r="J298" s="1"/>
-      <c r="K298" s="1"/>
-    </row>
-    <row r="299" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C299" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="D299" s="269">
-        <f>D23/ABS(D28)</f>
-        <v>43.646272915512931</v>
-      </c>
-      <c r="E299" s="269">
-        <f>E23/ABS(E28)</f>
-        <v>69.062139074572443</v>
-      </c>
-      <c r="F299" s="269">
-        <f>F23/ABS(F28)</f>
-        <v>60.114135699581482</v>
-      </c>
-      <c r="G299" s="269">
-        <f>G23/ABS(G28)</f>
-        <v>67.041013734978748</v>
-      </c>
-      <c r="H299" s="269">
-        <f>H23/ABS(H28)</f>
-        <v>71.876792675225701</v>
-      </c>
-      <c r="I299" s="269">
-        <f>I23/ABS(I28)</f>
-        <v>75.684630154587666</v>
-      </c>
-      <c r="J299" s="269">
-        <f>J23/ABS(J28)</f>
-        <v>80.036496388476451</v>
-      </c>
-      <c r="K299" s="269">
-        <f>K23/ABS(K28)</f>
-        <v>83.107284413177169</v>
-      </c>
-    </row>
-    <row r="300" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C300" s="13" t="s">
+      <c r="D302" s="6"/>
+    </row>
+    <row r="303" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C303" s="17" t="s">
+        <v>291</v>
+      </c>
+      <c r="D303" s="269">
+        <f t="shared" ref="D303:K303" si="210">D57/D81</f>
+        <v>5.77411542971761</v>
+      </c>
+      <c r="E303" s="269">
+        <f t="shared" si="210"/>
+        <v>5.3226126935625597</v>
+      </c>
+      <c r="F303" s="269">
+        <f t="shared" si="210"/>
+        <v>3.3913703598340623</v>
+      </c>
+      <c r="G303" s="269">
+        <f t="shared" si="210"/>
+        <v>3.3074457383168001</v>
+      </c>
+      <c r="H303" s="269">
+        <f t="shared" si="210"/>
+        <v>3.4606490144925535</v>
+      </c>
+      <c r="I303" s="269">
+        <f t="shared" si="210"/>
+        <v>3.8044943846366581</v>
+      </c>
+      <c r="J303" s="269">
+        <f t="shared" si="210"/>
+        <v>4.0520093723822015</v>
+      </c>
+      <c r="K303" s="269">
+        <f t="shared" si="210"/>
+        <v>4.3649928560117939</v>
+      </c>
+      <c r="L303" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="304" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C304" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="D304" s="269">
+        <f t="shared" ref="D304:K304" si="211">(D57-D51)/D81</f>
+        <v>3.500929243248466</v>
+      </c>
+      <c r="E304" s="269">
+        <f t="shared" si="211"/>
+        <v>2.6070767661500693</v>
+      </c>
+      <c r="F304" s="269">
+        <f t="shared" si="211"/>
+        <v>1.3164074461059094</v>
+      </c>
+      <c r="G304" s="269">
+        <f t="shared" si="211"/>
+        <v>1.2617076774749638</v>
+      </c>
+      <c r="H304" s="269">
+        <f t="shared" si="211"/>
+        <v>1.3067526724357721</v>
+      </c>
+      <c r="I304" s="269">
+        <f t="shared" si="211"/>
+        <v>1.4344098767492668</v>
+      </c>
+      <c r="J304" s="269">
+        <f t="shared" si="211"/>
+        <v>1.6205264434263638</v>
+      </c>
+      <c r="K304" s="269">
+        <f t="shared" si="211"/>
+        <v>1.8881340594823481</v>
+      </c>
+      <c r="L304" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="305" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C305" s="17"/>
+      <c r="D305" s="269"/>
+      <c r="E305" s="269"/>
+      <c r="F305" s="269"/>
+      <c r="G305" s="269"/>
+      <c r="H305" s="269"/>
+      <c r="I305" s="269"/>
+      <c r="J305" s="269"/>
+      <c r="K305" s="269"/>
+    </row>
+    <row r="306" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C306" s="13" t="s">
         <v>298</v>
       </c>
-      <c r="D300" s="6"/>
-    </row>
-    <row r="301" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C301" s="17" t="s">
-        <v>291</v>
-      </c>
-      <c r="D301" s="269">
-        <f>D57/D81</f>
-        <v>5.77411542971761</v>
-      </c>
-      <c r="E301" s="269">
-        <f>E57/E81</f>
-        <v>5.3226126935625597</v>
-      </c>
-      <c r="F301" s="269">
-        <f>F57/F81</f>
-        <v>3.3913703598340623</v>
-      </c>
-      <c r="G301" s="269">
-        <f>G57/G81</f>
-        <v>2.2361358429515428</v>
-      </c>
-      <c r="H301" s="269">
-        <f>H57/H81</f>
-        <v>1.7797406985926982</v>
-      </c>
-      <c r="I301" s="269">
-        <f>I57/I81</f>
-        <v>1.5391443324993515</v>
-      </c>
-      <c r="J301" s="269">
-        <f>J57/J81</f>
-        <v>1.3978644180397348</v>
-      </c>
-      <c r="K301" s="269">
-        <f>K57/K81</f>
-        <v>1.311465523933101</v>
-      </c>
-    </row>
-    <row r="302" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C302" s="17" t="s">
-        <v>292</v>
-      </c>
-      <c r="D302" s="269">
-        <f>(D57-D51)/D81</f>
-        <v>3.500929243248466</v>
-      </c>
-      <c r="E302" s="269">
-        <f>(E57-E51)/E81</f>
-        <v>2.6070767661500693</v>
-      </c>
-      <c r="F302" s="269">
-        <f>(F57-F51)/F81</f>
-        <v>1.3164074461059094</v>
-      </c>
-      <c r="G302" s="269">
-        <f>(G57-G51)/G81</f>
-        <v>0.85302979524154821</v>
-      </c>
-      <c r="H302" s="269">
-        <f>(H57-H51)/H81</f>
-        <v>0.67203605577716718</v>
-      </c>
-      <c r="I302" s="269">
-        <f>(I57-I51)/I81</f>
-        <v>0.57662181458319084</v>
-      </c>
-      <c r="J302" s="269">
-        <f>(J57-J51)/J81</f>
-        <v>0.52059686128891591</v>
-      </c>
-      <c r="K302" s="269">
-        <f>(K57-K51)/K81</f>
-        <v>0.48635219885586917</v>
-      </c>
-    </row>
-    <row r="303" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="D303" s="269"/>
-      <c r="E303" s="269"/>
-      <c r="F303" s="269"/>
-      <c r="G303" s="269"/>
-      <c r="H303" s="269"/>
-      <c r="I303" s="269"/>
-      <c r="J303" s="269"/>
-      <c r="K303" s="269"/>
-    </row>
-    <row r="304" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C304" s="6" t="s">
+      <c r="D306" s="269"/>
+      <c r="E306" s="269"/>
+      <c r="F306" s="269"/>
+      <c r="G306" s="269"/>
+      <c r="H306" s="269"/>
+      <c r="I306" s="269"/>
+      <c r="J306" s="269"/>
+      <c r="K306" s="269"/>
+    </row>
+    <row r="307" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C307" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="D307" s="211">
+        <f t="shared" ref="D307:K307" si="212">D31/D69</f>
+        <v>7.8662585664128565E-2</v>
+      </c>
+      <c r="E307" s="211">
+        <f t="shared" si="212"/>
+        <v>9.2230767453665444E-2</v>
+      </c>
+      <c r="F307" s="211">
+        <f t="shared" si="212"/>
+        <v>8.3312091515725592E-2</v>
+      </c>
+      <c r="G307" s="211">
+        <f t="shared" si="212"/>
+        <v>8.074547040408861E-2</v>
+      </c>
+      <c r="H307" s="211">
+        <f t="shared" si="212"/>
+        <v>8.2011163610444374E-2</v>
+      </c>
+      <c r="I307" s="211">
+        <f t="shared" si="212"/>
+        <v>8.2383231137708693E-2</v>
+      </c>
+      <c r="J307" s="211">
+        <f t="shared" si="212"/>
+        <v>8.2558122376208298E-2</v>
+      </c>
+      <c r="K307" s="211">
+        <f t="shared" si="212"/>
+        <v>8.1387673353890869E-2</v>
+      </c>
+      <c r="L307" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="308" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C308" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="D308" s="211">
+        <f t="shared" ref="D308:K308" si="213">D31/D98</f>
+        <v>8.9894646776820658E-2</v>
+      </c>
+      <c r="E308" s="211">
+        <f t="shared" si="213"/>
+        <v>0.1045367050808837</v>
+      </c>
+      <c r="F308" s="211">
+        <f t="shared" si="213"/>
+        <v>9.7801197704850074E-2</v>
+      </c>
+      <c r="G308" s="211">
+        <f t="shared" si="213"/>
+        <v>9.5544549554126598E-2</v>
+      </c>
+      <c r="H308" s="211">
+        <f t="shared" si="213"/>
+        <v>9.6709731002251012E-2</v>
+      </c>
+      <c r="I308" s="211">
+        <f t="shared" si="213"/>
+        <v>9.6114739341206179E-2</v>
+      </c>
+      <c r="J308" s="211">
+        <f t="shared" si="213"/>
+        <v>9.5909101100631416E-2</v>
+      </c>
+      <c r="K308" s="211">
+        <f t="shared" si="213"/>
+        <v>9.4057792222588713E-2</v>
+      </c>
+      <c r="L308" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="309" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C309" s="17"/>
+      <c r="D309" s="211"/>
+      <c r="E309" s="211"/>
+      <c r="F309" s="211"/>
+      <c r="G309" s="211"/>
+      <c r="H309" s="211"/>
+      <c r="I309" s="211"/>
+      <c r="J309" s="211"/>
+      <c r="K309" s="211"/>
+    </row>
+    <row r="310" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C310" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="D310" s="269"/>
+      <c r="E310" s="269"/>
+      <c r="F310" s="269"/>
+      <c r="G310" s="269"/>
+      <c r="H310" s="269"/>
+      <c r="I310" s="269"/>
+      <c r="J310" s="269"/>
+      <c r="K310" s="269"/>
+    </row>
+    <row r="311" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C311" s="17" t="s">
+        <v>302</v>
+      </c>
+      <c r="D311" s="211">
+        <f t="shared" ref="D311:K311" si="214">D31/D16</f>
+        <v>0.24328388410614471</v>
+      </c>
+      <c r="E311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.29712452854104449</v>
+      </c>
+      <c r="F311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.22935869819746624</v>
+      </c>
+      <c r="G311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.21096574959993467</v>
+      </c>
+      <c r="H311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.20664722316693837</v>
+      </c>
+      <c r="I311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.2022572476466229</v>
+      </c>
+      <c r="J311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.20240449934987922</v>
+      </c>
+      <c r="K311" s="211">
+        <f t="shared" si="214"/>
+        <v>0.20249912376952711</v>
+      </c>
+      <c r="L311" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="312" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C312" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="D312" s="269">
+        <f t="shared" ref="D312:K312" si="215">D16/D69</f>
+        <v>0.32333660716222407</v>
+      </c>
+      <c r="E312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.31041115288105459</v>
+      </c>
+      <c r="F312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.36323929360637591</v>
+      </c>
+      <c r="G312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.38274208281301797</v>
+      </c>
+      <c r="H312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.39686554870467472</v>
+      </c>
+      <c r="I312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.40731905578803246</v>
+      </c>
+      <c r="J312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.40788679422336943</v>
+      </c>
+      <c r="K312" s="269">
+        <f t="shared" si="215"/>
+        <v>0.40191617543254976</v>
+      </c>
+      <c r="L312" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="313" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C313" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="D313" s="269">
+        <f t="shared" ref="D313:K313" si="216">D69/D98</f>
+        <v>1.142787845299803</v>
+      </c>
+      <c r="E313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1334255147925605</v>
+      </c>
+      <c r="F313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1739136051624581</v>
+      </c>
+      <c r="G313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1832806109863052</v>
+      </c>
+      <c r="H313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1792264216811421</v>
+      </c>
+      <c r="I313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1666784370297933</v>
+      </c>
+      <c r="J313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1617161139346674</v>
+      </c>
+      <c r="K313" s="269">
+        <f t="shared" si="216"/>
+        <v>1.1556761404593234</v>
+      </c>
+    </row>
+    <row r="314" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C314" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="D314" s="211">
+        <f>D311*D312*D313</f>
+        <v>8.9894646776820658E-2</v>
+      </c>
+      <c r="E314" s="211">
+        <f t="shared" ref="E314:K314" si="217">E311*E312*E313</f>
+        <v>0.10453670508088367</v>
+      </c>
+      <c r="F314" s="211">
+        <f t="shared" si="217"/>
+        <v>9.7801197704850087E-2</v>
+      </c>
+      <c r="G314" s="211">
+        <f t="shared" si="217"/>
+        <v>9.5544549554126598E-2</v>
+      </c>
+      <c r="H314" s="211">
+        <f t="shared" si="217"/>
+        <v>9.6709731002250998E-2</v>
+      </c>
+      <c r="I314" s="211">
+        <f t="shared" si="217"/>
+        <v>9.6114739341206179E-2</v>
+      </c>
+      <c r="J314" s="211">
+        <f t="shared" si="217"/>
+        <v>9.5909101100631416E-2</v>
+      </c>
+      <c r="K314" s="211">
+        <f t="shared" si="217"/>
+        <v>9.4057792222588713E-2</v>
+      </c>
+    </row>
+    <row r="315" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C315" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D315" s="188">
+        <f t="shared" ref="D315:K315" si="218">D314-D308</f>
+        <v>0</v>
+      </c>
+      <c r="E315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+      <c r="F315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+      <c r="G315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+      <c r="H315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+      <c r="I315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+      <c r="J315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+      <c r="K315" s="188">
+        <f t="shared" si="218"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="D316" s="269"/>
+      <c r="E316" s="269"/>
+      <c r="F316" s="269"/>
+      <c r="G316" s="269"/>
+      <c r="H316" s="269"/>
+      <c r="I316" s="269"/>
+      <c r="J316" s="269"/>
+      <c r="K316" s="269"/>
+    </row>
+    <row r="317" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C317" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D304" s="28" t="str">
-        <f>IF(AND(D295&lt;1.5, D302&gt;1), "Strong", IF(D295&lt;3, "Adequate", "Elevated"))</f>
+      <c r="D317" s="28" t="str">
+        <f t="shared" ref="D317:K317" si="219">IF(AND(D295&lt;1.5, D304&gt;1), "Strong", IF(D295&lt;3, "Adequate", "Elevated"))</f>
         <v>Strong</v>
       </c>
-      <c r="E304" s="28" t="str">
-        <f t="shared" ref="E304:K304" si="204">IF(AND(E295&lt;1.5, E302&gt;1), "Strong", IF(E295&lt;3, "Adequate", "Elevated"))</f>
+      <c r="E317" s="28" t="str">
+        <f t="shared" si="219"/>
         <v>Strong</v>
       </c>
-      <c r="F304" s="28" t="str">
-        <f t="shared" si="204"/>
+      <c r="F317" s="28" t="str">
+        <f t="shared" si="219"/>
         <v>Strong</v>
       </c>
-      <c r="G304" s="28" t="str">
-        <f t="shared" si="204"/>
-        <v>Adequate</v>
-      </c>
-      <c r="H304" s="28" t="str">
-        <f t="shared" si="204"/>
-        <v>Adequate</v>
-      </c>
-      <c r="I304" s="28" t="str">
-        <f t="shared" si="204"/>
-        <v>Adequate</v>
-      </c>
-      <c r="J304" s="28" t="str">
-        <f t="shared" si="204"/>
-        <v>Adequate</v>
-      </c>
-      <c r="K304" s="28" t="str">
-        <f t="shared" si="204"/>
-        <v>Adequate</v>
+      <c r="G317" s="28" t="str">
+        <f t="shared" si="219"/>
+        <v>Strong</v>
+      </c>
+      <c r="H317" s="28" t="str">
+        <f t="shared" si="219"/>
+        <v>Strong</v>
+      </c>
+      <c r="I317" s="28" t="str">
+        <f t="shared" si="219"/>
+        <v>Strong</v>
+      </c>
+      <c r="J317" s="28" t="str">
+        <f t="shared" si="219"/>
+        <v>Strong</v>
+      </c>
+      <c r="K317" s="28" t="str">
+        <f t="shared" si="219"/>
+        <v>Strong</v>
       </c>
     </row>
   </sheetData>
